--- a/Data/Master_Input.xlsx
+++ b/Data/Master_Input.xlsx
@@ -3,21 +3,21 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Global_Parameters" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Scenario_Parameters" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,11 +37,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <b val="1"/>
     </font>
   </fonts>
@@ -53,27 +48,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -107,10 +87,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -481,16 +459,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20.140625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="69.42578125" bestFit="1" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -526,55 +508,63 @@
           <t>Valuation Date</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2024-12-31 00:00:00</t>
-        </is>
+      <c r="B4" s="2" t="n">
+        <v>45657</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Projection Years</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+          <t>First IPD</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45747</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Projection Frequency</t>
+          <t>Projection Years</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Output Filepath</t>
+          <t>Projection Frequency</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>output.xlsx</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Output Filepath</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>output.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Output Frequency</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -591,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,40 +617,45 @@
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mortality Improvement</t>
+          <t>Female Mortality Improvement</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
+          <t>Male Mortality Improvement</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
           <t>Sales Cost</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Property Haircut</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Settlement Delay (Alive)</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Settlement Delay (Dead)</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Rational VER?</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Valuation Method</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>NNEG Approach</t>
         </is>
@@ -699,32 +694,37 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>aa_mortality_improvement.csv</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
+          <t>base_f_mortality_improvement.csv</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>base_m_mortality_improvement.csv</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.02</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Moodys</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
@@ -766,29 +766,34 @@
           <t>aa_mortality_improvement.csv</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>aa_mortality_improvement.csv</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.02</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>12</v>
       </c>
       <c r="K3" t="n">
         <v>12</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Moodys</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
@@ -830,29 +835,34 @@
           <t>aa_mortality_improvement.csv</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>aa_mortality_improvement.csv</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.02</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Moodys</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
@@ -894,29 +904,34 @@
           <t>aa_mortality_improvement.csv</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>aa_mortality_improvement.csv</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.02</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.1</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>6</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Moodys</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
@@ -958,29 +973,34 @@
           <t>aa_mortality_improvement.csv</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>aa_mortality_improvement.csv</t>
+        </is>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>12</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="n">
+        <v>12</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Moodys</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
@@ -1022,29 +1042,34 @@
           <t>aa_mortality_improvement.csv</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>aa_mortality_improvement.csv</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.02</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>0.1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>12</v>
       </c>
       <c r="K7" t="n">
         <v>12</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="n">
+        <v>12</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Moodys</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
@@ -1086,29 +1111,34 @@
           <t>aa_mortality_improvement.csv</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>aa_mortality_improvement.csv</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.02</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>0.1</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>6</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Moodys</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
@@ -1150,29 +1180,34 @@
           <t>aa_mortality_improvement.csv</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>aa_mortality_improvement.csv</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.02</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>0.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>12</v>
       </c>
       <c r="K9" t="n">
         <v>12</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="n">
+        <v>12</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Moodys</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
@@ -1214,29 +1249,34 @@
           <t>aa_mortality_improvement.csv</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>aa_mortality_improvement.csv</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.02</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>0.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Moodys</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
@@ -1278,29 +1318,34 @@
           <t>aa_mortality_improvement.csv</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>aa_mortality_improvement.csv</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.02</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>0.1</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>6</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Moodys</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
@@ -1342,29 +1387,34 @@
           <t>aa_mortality_improvement.csv</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>aa_mortality_improvement.csv</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>0.02</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>0.1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>12</v>
       </c>
       <c r="K12" t="n">
         <v>12</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="n">
+        <v>12</v>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Moodys</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
@@ -1406,29 +1456,34 @@
           <t>aa_mortality_improvement.csv</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>aa_mortality_improvement.csv</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>0.02</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>0.1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Moodys</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
@@ -1470,29 +1525,34 @@
           <t>aa_mortality_improvement.csv</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>aa_mortality_improvement.csv</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>0.02</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>0.1</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>6</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Moodys</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
@@ -1534,29 +1594,34 @@
           <t>aa_mortality_improvement.csv</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>aa_mortality_improvement.csv</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>0.02</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>0.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>12</v>
       </c>
       <c r="K15" t="n">
         <v>12</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" t="n">
+        <v>12</v>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Moodys</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
@@ -1598,29 +1663,34 @@
           <t>aa_mortality_improvement.csv</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>aa_mortality_improvement.csv</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>0.02</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>0.1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Moodys</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
@@ -1662,29 +1732,34 @@
           <t>aa_mortality_improvement.csv</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>aa_mortality_improvement.csv</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>0.02</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>0.1</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>6</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Moodys</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
